--- a/MomijiStore_OS/02_Analytics/SourceData/Amazon運営 KPI管理シート.xlsx
+++ b/MomijiStore_OS/02_Analytics/SourceData/Amazon運営 KPI管理シート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hide0726/Desktop/Claude Code/MomijiStore_OS/02_Analytics/SourceData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_0CBC4F679679ACEEE86050775F2D1E7D59F10250" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_CDB2ED489246002E6222E4D44D2D1E7D29FF68AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51200" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7月" sheetId="1" r:id="rId1"/>
@@ -3432,7 +3432,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3458,18 +3458,19 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3490,8 +3491,8 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3797,7 +3798,7 @@
   <dimension ref="A1:O361"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="1" max="1" width="46.6640625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="4" width="13" customWidth="1"/>
   </cols>
@@ -5975,7 +5976,7 @@
       </c>
     </row>
     <row r="49" spans="1:15">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -6009,18 +6010,20 @@
       <c r="K49" s="1">
         <v>4703</v>
       </c>
-      <c r="L49" s="5"/>
+      <c r="L49" s="1">
+        <v>2072</v>
+      </c>
       <c r="M49" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20720</v>
       </c>
       <c r="N49" s="1">
         <f t="shared" si="2"/>
-        <v>36438</v>
+        <v>15718</v>
       </c>
       <c r="O49" s="4">
         <f t="shared" si="3"/>
-        <v>0.88568581220680098</v>
+        <v>0.38205196762353855</v>
       </c>
     </row>
     <row r="50" spans="1:15">
@@ -7384,18 +7387,20 @@
       <c r="K76" s="1">
         <v>2427</v>
       </c>
-      <c r="L76" s="5"/>
+      <c r="L76" s="1">
+        <v>840</v>
+      </c>
       <c r="M76" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15960</v>
       </c>
       <c r="N76" s="1">
         <f t="shared" si="6"/>
-        <v>23793</v>
+        <v>7833</v>
       </c>
       <c r="O76" s="4">
         <f t="shared" si="7"/>
-        <v>0.90743707093821513</v>
+        <v>0.29874141876430205</v>
       </c>
     </row>
     <row r="77" spans="1:15">
@@ -7637,18 +7642,20 @@
       <c r="K81" s="1">
         <v>2624</v>
       </c>
-      <c r="L81" s="5"/>
+      <c r="L81" s="1">
+        <v>1030</v>
+      </c>
       <c r="M81" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13390</v>
       </c>
       <c r="N81" s="1">
         <f t="shared" si="6"/>
-        <v>22156</v>
+        <v>8766</v>
       </c>
       <c r="O81" s="4">
         <f t="shared" si="7"/>
-        <v>0.89410815173527036</v>
+        <v>0.35375302663438257</v>
       </c>
     </row>
     <row r="82" spans="1:15">
@@ -7907,7 +7914,7 @@
       </c>
     </row>
     <row r="87" spans="1:15">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="6" t="s">
         <v>279</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -7941,22 +7948,24 @@
       <c r="K87" s="1">
         <v>2553</v>
       </c>
-      <c r="L87" s="5"/>
+      <c r="L87" s="1">
+        <v>4248</v>
+      </c>
       <c r="M87" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16992</v>
       </c>
       <c r="N87" s="1">
         <f t="shared" si="6"/>
-        <v>19765</v>
+        <v>2773</v>
       </c>
       <c r="O87" s="4">
         <f t="shared" si="7"/>
-        <v>0.88560802939331484</v>
+        <v>0.12424948472085312</v>
       </c>
     </row>
     <row r="88" spans="1:15">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="6" t="s">
         <v>282</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -8415,7 +8424,7 @@
       </c>
     </row>
     <row r="97" spans="1:15">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="6" t="s">
         <v>312</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -8449,22 +8458,24 @@
       <c r="K97" s="1">
         <v>1570</v>
       </c>
-      <c r="L97" s="5"/>
+      <c r="L97" s="1">
+        <v>253</v>
+      </c>
       <c r="M97" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4807</v>
       </c>
       <c r="N97" s="1">
         <f t="shared" si="6"/>
-        <v>17411</v>
+        <v>12604</v>
       </c>
       <c r="O97" s="4">
         <f t="shared" si="7"/>
-        <v>0.91728570675939092</v>
+        <v>0.66403245350613771</v>
       </c>
     </row>
     <row r="98" spans="1:15">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="6" t="s">
         <v>315</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -8498,18 +8509,20 @@
       <c r="K98" s="1">
         <v>3196</v>
       </c>
-      <c r="L98" s="5"/>
+      <c r="L98" s="1">
+        <v>274</v>
+      </c>
       <c r="M98" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5206</v>
       </c>
       <c r="N98" s="1">
         <f t="shared" si="6"/>
-        <v>15704</v>
+        <v>10498</v>
       </c>
       <c r="O98" s="4">
         <f t="shared" si="7"/>
-        <v>0.83089947089947092</v>
+        <v>0.55544973544973542</v>
       </c>
     </row>
     <row r="99" spans="1:15">
@@ -9006,7 +9019,9 @@
       <c r="K108" s="1">
         <v>2016</v>
       </c>
-      <c r="L108" s="5"/>
+      <c r="L108" s="1">
+        <v>0</v>
+      </c>
       <c r="M108" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -9021,7 +9036,7 @@
       </c>
     </row>
     <row r="109" spans="1:15">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="6" t="s">
         <v>354</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -9055,18 +9070,20 @@
       <c r="K109" s="1">
         <v>2976</v>
       </c>
-      <c r="L109" s="5"/>
+      <c r="L109" s="1">
+        <v>274</v>
+      </c>
       <c r="M109" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4384</v>
       </c>
       <c r="N109" s="1">
         <f t="shared" si="6"/>
-        <v>14624</v>
+        <v>10240</v>
       </c>
       <c r="O109" s="4">
         <f t="shared" si="7"/>
-        <v>0.83090909090909093</v>
+        <v>0.58181818181818179</v>
       </c>
     </row>
     <row r="110" spans="1:15">
@@ -9359,18 +9376,20 @@
       <c r="K115" s="1">
         <v>881</v>
       </c>
-      <c r="L115" s="5"/>
+      <c r="L115" s="1">
+        <v>274</v>
+      </c>
       <c r="M115" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5754</v>
       </c>
       <c r="N115" s="1">
         <f t="shared" si="6"/>
-        <v>14869</v>
+        <v>9115</v>
       </c>
       <c r="O115" s="4">
         <f t="shared" si="7"/>
-        <v>0.94406349206349205</v>
+        <v>0.57873015873015876</v>
       </c>
     </row>
     <row r="116" spans="1:15">
@@ -9578,7 +9597,7 @@
       </c>
     </row>
     <row r="120" spans="1:15">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="6" t="s">
         <v>389</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -9612,18 +9631,20 @@
       <c r="K120" s="1">
         <v>792</v>
       </c>
-      <c r="L120" s="5"/>
+      <c r="L120" s="1">
+        <v>383</v>
+      </c>
       <c r="M120" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9192</v>
       </c>
       <c r="N120" s="1">
         <f t="shared" si="6"/>
-        <v>13548</v>
+        <v>4356</v>
       </c>
       <c r="O120" s="4">
         <f t="shared" si="7"/>
-        <v>0.94476987447698746</v>
+        <v>0.30376569037656903</v>
       </c>
     </row>
     <row r="121" spans="1:15">
@@ -9661,18 +9682,20 @@
       <c r="K121" s="1">
         <v>1320</v>
       </c>
-      <c r="L121" s="5"/>
+      <c r="L121" s="1">
+        <v>471</v>
+      </c>
       <c r="M121" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5652</v>
       </c>
       <c r="N121" s="1">
         <f t="shared" si="6"/>
-        <v>12960</v>
+        <v>7308</v>
       </c>
       <c r="O121" s="4">
         <f t="shared" si="7"/>
-        <v>0.90756302521008403</v>
+        <v>0.5117647058823529</v>
       </c>
     </row>
     <row r="122" spans="1:15">
@@ -11716,7 +11739,7 @@
       </c>
     </row>
     <row r="162" spans="1:15">
-      <c r="A162" s="1" t="s">
+      <c r="A162" s="6" t="s">
         <v>530</v>
       </c>
       <c r="B162" s="1" t="s">
@@ -11750,18 +11773,20 @@
       <c r="K162" s="1">
         <v>833</v>
       </c>
-      <c r="L162" s="5"/>
+      <c r="L162" s="1">
+        <v>1104</v>
+      </c>
       <c r="M162" s="1">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6624</v>
       </c>
       <c r="N162" s="1">
         <f t="shared" si="10"/>
-        <v>8167</v>
+        <v>1543</v>
       </c>
       <c r="O162" s="4">
         <f t="shared" si="11"/>
-        <v>0.9074444444444445</v>
+        <v>0.17144444444444445</v>
       </c>
     </row>
     <row r="163" spans="1:15">
@@ -13958,7 +13983,7 @@
       </c>
     </row>
     <row r="206" spans="1:15">
-      <c r="A206" s="1" t="s">
+      <c r="A206" s="6" t="s">
         <v>674</v>
       </c>
       <c r="B206" s="1" t="s">
@@ -13992,18 +14017,20 @@
       <c r="K206" s="1">
         <v>604</v>
       </c>
-      <c r="L206" s="5"/>
+      <c r="L206" s="1">
+        <v>1062</v>
+      </c>
       <c r="M206" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3186</v>
       </c>
       <c r="N206" s="1">
         <f t="shared" si="14"/>
-        <v>4676</v>
+        <v>1490</v>
       </c>
       <c r="O206" s="4">
         <f t="shared" si="15"/>
-        <v>0.88560606060606062</v>
+        <v>0.28219696969696972</v>
       </c>
     </row>
     <row r="207" spans="1:15">
@@ -14194,7 +14221,9 @@
       <c r="K210" s="1">
         <v>572</v>
       </c>
-      <c r="L210" s="5"/>
+      <c r="L210" s="1">
+        <v>0</v>
+      </c>
       <c r="M210" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14311,7 +14340,7 @@
       </c>
     </row>
     <row r="213" spans="1:15">
-      <c r="A213" s="1" t="s">
+      <c r="A213" s="6" t="s">
         <v>354</v>
       </c>
       <c r="B213" s="1" t="s">
@@ -14345,18 +14374,20 @@
       <c r="K213" s="1">
         <v>830</v>
       </c>
-      <c r="L213" s="5"/>
+      <c r="L213" s="1">
+        <v>274</v>
+      </c>
       <c r="M213" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1370</v>
       </c>
       <c r="N213" s="1">
         <f t="shared" si="14"/>
-        <v>4070</v>
+        <v>2700</v>
       </c>
       <c r="O213" s="4">
         <f t="shared" si="15"/>
-        <v>0.83061224489795915</v>
+        <v>0.55102040816326525</v>
       </c>
     </row>
     <row r="214" spans="1:15">
@@ -14394,18 +14425,20 @@
       <c r="K214" s="1">
         <v>1628</v>
       </c>
-      <c r="L214" s="5"/>
+      <c r="L214" s="1">
+        <v>471</v>
+      </c>
       <c r="M214" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1884</v>
       </c>
       <c r="N214" s="1">
         <f t="shared" si="14"/>
-        <v>3172</v>
+        <v>1288</v>
       </c>
       <c r="O214" s="4">
         <f t="shared" si="15"/>
-        <v>0.66083333333333338</v>
+        <v>0.26833333333333331</v>
       </c>
     </row>
     <row r="215" spans="1:15">
@@ -14545,18 +14578,20 @@
       <c r="K217" s="1">
         <v>771</v>
       </c>
-      <c r="L217" s="5"/>
+      <c r="L217" s="1">
+        <v>3940</v>
+      </c>
       <c r="M217" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3940</v>
       </c>
       <c r="N217" s="1">
         <f t="shared" si="14"/>
-        <v>3783</v>
+        <v>-157</v>
       </c>
       <c r="O217" s="4">
         <f t="shared" si="15"/>
-        <v>0.83069828722002637</v>
+        <v>-3.4475186649099696E-2</v>
       </c>
     </row>
     <row r="218" spans="1:15">
@@ -15325,7 +15360,7 @@
       </c>
     </row>
     <row r="233" spans="1:15">
-      <c r="A233" s="1" t="s">
+      <c r="A233" s="6" t="s">
         <v>756</v>
       </c>
       <c r="B233" s="1" t="s">
@@ -15359,18 +15394,20 @@
       <c r="K233" s="1">
         <v>644</v>
       </c>
-      <c r="L233" s="5"/>
+      <c r="L233" s="1">
+        <v>255</v>
+      </c>
       <c r="M233" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="N233" s="1">
         <f t="shared" si="14"/>
-        <v>3156</v>
+        <v>2136</v>
       </c>
       <c r="O233" s="4">
         <f t="shared" si="15"/>
-        <v>0.83052631578947367</v>
+        <v>0.56210526315789477</v>
       </c>
     </row>
     <row r="234" spans="1:15">
@@ -16241,7 +16278,7 @@
       </c>
     </row>
     <row r="251" spans="1:15">
-      <c r="A251" s="1" t="s">
+      <c r="A251" s="6" t="s">
         <v>816</v>
       </c>
       <c r="B251" s="1" t="s">
@@ -16275,18 +16312,20 @@
       <c r="K251" s="1">
         <v>351</v>
       </c>
-      <c r="L251" s="5"/>
+      <c r="L251" s="1">
+        <v>1911</v>
+      </c>
       <c r="M251" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1911</v>
       </c>
       <c r="N251" s="1">
         <f t="shared" si="14"/>
-        <v>2717</v>
+        <v>806</v>
       </c>
       <c r="O251" s="4">
         <f t="shared" si="15"/>
-        <v>0.88559322033898302</v>
+        <v>0.26271186440677968</v>
       </c>
     </row>
     <row r="252" spans="1:15">
@@ -17361,7 +17400,7 @@
       </c>
     </row>
     <row r="273" spans="1:15">
-      <c r="A273" s="1" t="s">
+      <c r="A273" s="6" t="s">
         <v>883</v>
       </c>
       <c r="B273" s="1" t="s">
@@ -17395,18 +17434,20 @@
       <c r="K273" s="1">
         <v>1144</v>
       </c>
-      <c r="L273" s="5"/>
+      <c r="L273" s="1">
+        <v>328</v>
+      </c>
       <c r="M273" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1312</v>
       </c>
       <c r="N273" s="1">
         <f t="shared" si="18"/>
-        <v>1372</v>
+        <v>60</v>
       </c>
       <c r="O273" s="4">
         <f t="shared" si="19"/>
-        <v>0.54531001589825123</v>
+        <v>2.3847376788553261E-2</v>
       </c>
     </row>
     <row r="274" spans="1:15">
@@ -17801,18 +17842,20 @@
       <c r="K281" s="1">
         <v>214</v>
       </c>
-      <c r="L281" s="5"/>
+      <c r="L281" s="1">
+        <v>612</v>
+      </c>
       <c r="M281" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1224</v>
       </c>
       <c r="N281" s="1">
         <f t="shared" si="18"/>
-        <v>2090</v>
+        <v>866</v>
       </c>
       <c r="O281" s="4">
         <f t="shared" si="19"/>
-        <v>0.90711805555555558</v>
+        <v>0.37586805555555558</v>
       </c>
     </row>
     <row r="282" spans="1:15">
@@ -17848,7 +17891,9 @@
       <c r="K282" s="1">
         <v>386</v>
       </c>
-      <c r="L282" s="5"/>
+      <c r="L282" s="1">
+        <v>0</v>
+      </c>
       <c r="M282" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -18305,18 +18350,20 @@
       <c r="K291" s="1">
         <v>320</v>
       </c>
-      <c r="L291" s="5"/>
+      <c r="L291" s="1">
+        <v>1500</v>
+      </c>
       <c r="M291" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N291" s="1">
         <f t="shared" si="18"/>
-        <v>1570</v>
+        <v>70</v>
       </c>
       <c r="O291" s="4">
         <f t="shared" si="19"/>
-        <v>0.8306878306878307</v>
+        <v>3.7037037037037035E-2</v>
       </c>
     </row>
     <row r="292" spans="1:15">
@@ -18371,7 +18418,7 @@
       </c>
     </row>
     <row r="293" spans="1:15">
-      <c r="A293" s="1" t="s">
+      <c r="A293" s="6" t="s">
         <v>945</v>
       </c>
       <c r="B293" s="1" t="s">
@@ -18405,7 +18452,9 @@
       <c r="K293" s="1">
         <v>212</v>
       </c>
-      <c r="L293" s="5"/>
+      <c r="L293" s="1">
+        <v>0</v>
+      </c>
       <c r="M293" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
@@ -18573,7 +18622,7 @@
       </c>
     </row>
     <row r="297" spans="1:15">
-      <c r="A297" s="1" t="s">
+      <c r="A297" s="6" t="s">
         <v>959</v>
       </c>
       <c r="B297" s="1" t="s">
@@ -18607,18 +18656,20 @@
       <c r="K297" s="1">
         <v>305</v>
       </c>
-      <c r="L297" s="5"/>
+      <c r="L297" s="1">
+        <v>811</v>
+      </c>
       <c r="M297" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="N297" s="1">
         <f t="shared" si="18"/>
-        <v>1494</v>
+        <v>683</v>
       </c>
       <c r="O297" s="4">
         <f t="shared" si="19"/>
-        <v>0.83046136742634802</v>
+        <v>0.37965536409116174</v>
       </c>
     </row>
     <row r="298" spans="1:15">
@@ -18877,7 +18928,7 @@
       </c>
     </row>
     <row r="303" spans="1:15">
-      <c r="A303" s="1" t="s">
+      <c r="A303" s="6" t="s">
         <v>980</v>
       </c>
       <c r="B303" s="1" t="s">
@@ -18911,18 +18962,20 @@
       <c r="K303" s="1">
         <v>84</v>
       </c>
-      <c r="L303" s="5"/>
+      <c r="L303" s="1">
+        <v>604</v>
+      </c>
       <c r="M303" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1208</v>
       </c>
       <c r="N303" s="1">
         <f t="shared" si="18"/>
-        <v>1416</v>
+        <v>208</v>
       </c>
       <c r="O303" s="4">
         <f t="shared" si="19"/>
-        <v>0.94399999999999995</v>
+        <v>0.13866666666666666</v>
       </c>
     </row>
     <row r="304" spans="1:15">
@@ -19079,7 +19132,7 @@
       </c>
     </row>
     <row r="307" spans="1:15">
-      <c r="A307" s="1" t="s">
+      <c r="A307" s="6" t="s">
         <v>991</v>
       </c>
       <c r="B307" s="1" t="s">
@@ -19113,22 +19166,24 @@
       <c r="K307" s="1">
         <v>139</v>
       </c>
-      <c r="L307" s="5"/>
+      <c r="L307" s="1">
+        <v>549</v>
+      </c>
       <c r="M307" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="N307" s="1">
         <f t="shared" si="18"/>
-        <v>1361</v>
+        <v>812</v>
       </c>
       <c r="O307" s="4">
         <f t="shared" si="19"/>
-        <v>0.90733333333333333</v>
+        <v>0.54133333333333333</v>
       </c>
     </row>
     <row r="308" spans="1:15">
-      <c r="A308" s="1" t="s">
+      <c r="A308" s="6" t="s">
         <v>995</v>
       </c>
       <c r="B308" s="1" t="s">
@@ -19162,22 +19217,24 @@
       <c r="K308" s="1">
         <v>139</v>
       </c>
-      <c r="L308" s="5"/>
+      <c r="L308" s="1">
+        <v>1482</v>
+      </c>
       <c r="M308" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1482</v>
       </c>
       <c r="N308" s="1">
         <f t="shared" si="18"/>
-        <v>1361</v>
+        <v>-121</v>
       </c>
       <c r="O308" s="4">
         <f t="shared" si="19"/>
-        <v>0.90733333333333333</v>
+        <v>-8.0666666666666664E-2</v>
       </c>
     </row>
     <row r="309" spans="1:15">
-      <c r="A309" s="1" t="s">
+      <c r="A309" s="6" t="s">
         <v>998</v>
       </c>
       <c r="B309" s="1" t="s">
@@ -19211,18 +19268,20 @@
       <c r="K309" s="1">
         <v>305</v>
       </c>
-      <c r="L309" s="5"/>
+      <c r="L309" s="1">
+        <v>1482</v>
+      </c>
       <c r="M309" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1482</v>
       </c>
       <c r="N309" s="1">
         <f t="shared" si="18"/>
-        <v>1195</v>
+        <v>-287</v>
       </c>
       <c r="O309" s="4">
         <f t="shared" si="19"/>
-        <v>0.79666666666666663</v>
+        <v>-0.19133333333333333</v>
       </c>
     </row>
     <row r="310" spans="1:15">
@@ -19260,22 +19319,24 @@
       <c r="K310" s="1">
         <v>139</v>
       </c>
-      <c r="L310" s="5"/>
+      <c r="L310" s="1">
+        <v>320</v>
+      </c>
       <c r="M310" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="N310" s="1">
         <f t="shared" si="18"/>
-        <v>1360</v>
+        <v>1040</v>
       </c>
       <c r="O310" s="4">
         <f t="shared" si="19"/>
-        <v>0.90727151434289521</v>
+        <v>0.69379586390927284</v>
       </c>
     </row>
     <row r="311" spans="1:15">
-      <c r="A311" s="1" t="s">
+      <c r="A311" s="6" t="s">
         <v>1004</v>
       </c>
       <c r="B311" s="1" t="s">
@@ -19309,18 +19370,20 @@
       <c r="K311" s="1">
         <v>139</v>
       </c>
-      <c r="L311" s="5"/>
+      <c r="L311" s="1">
+        <v>830</v>
+      </c>
       <c r="M311" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>830</v>
       </c>
       <c r="N311" s="1">
         <f t="shared" si="18"/>
-        <v>1359</v>
+        <v>529</v>
       </c>
       <c r="O311" s="4">
         <f t="shared" si="19"/>
-        <v>0.90720961281708945</v>
+        <v>0.35313751668891857</v>
       </c>
     </row>
     <row r="312" spans="1:15">
@@ -19358,18 +19421,20 @@
       <c r="K312" s="1">
         <v>139</v>
       </c>
-      <c r="L312" s="5"/>
+      <c r="L312" s="1">
+        <v>830</v>
+      </c>
       <c r="M312" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>830</v>
       </c>
       <c r="N312" s="1">
         <f t="shared" si="18"/>
-        <v>1359</v>
+        <v>529</v>
       </c>
       <c r="O312" s="4">
         <f t="shared" si="19"/>
-        <v>0.90720961281708945</v>
+        <v>0.35313751668891857</v>
       </c>
     </row>
     <row r="313" spans="1:15">
@@ -19407,18 +19472,20 @@
       <c r="K313" s="1">
         <v>138</v>
       </c>
-      <c r="L313" s="5"/>
+      <c r="L313" s="1">
+        <v>963</v>
+      </c>
       <c r="M313" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>963</v>
       </c>
       <c r="N313" s="1">
         <f t="shared" si="18"/>
-        <v>1347</v>
+        <v>384</v>
       </c>
       <c r="O313" s="4">
         <f t="shared" si="19"/>
-        <v>0.90707070707070703</v>
+        <v>0.25858585858585859</v>
       </c>
     </row>
     <row r="314" spans="1:15">
@@ -19864,18 +19931,20 @@
       <c r="K322" s="1">
         <v>110</v>
       </c>
-      <c r="L322" s="5"/>
+      <c r="L322" s="1">
+        <v>471</v>
+      </c>
       <c r="M322" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="N322" s="1">
         <f t="shared" si="18"/>
-        <v>1078</v>
+        <v>607</v>
       </c>
       <c r="O322" s="4">
         <f t="shared" si="19"/>
-        <v>0.90740740740740744</v>
+        <v>0.51094276094276092</v>
       </c>
     </row>
     <row r="323" spans="1:15">
@@ -20219,18 +20288,20 @@
       <c r="K329" s="1">
         <v>169</v>
       </c>
-      <c r="L329" s="5"/>
+      <c r="L329" s="1">
+        <v>242</v>
+      </c>
       <c r="M329" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="N329" s="1">
         <f t="shared" si="22"/>
-        <v>831</v>
+        <v>589</v>
       </c>
       <c r="O329" s="4">
         <f t="shared" si="23"/>
-        <v>0.83099999999999996</v>
+        <v>0.58899999999999997</v>
       </c>
     </row>
     <row r="330" spans="1:15">
@@ -20336,7 +20407,7 @@
       </c>
     </row>
     <row r="332" spans="1:15">
-      <c r="A332" s="1" t="s">
+      <c r="A332" s="6" t="s">
         <v>1069</v>
       </c>
       <c r="B332" s="1" t="s">
@@ -20370,22 +20441,24 @@
       <c r="K332" s="1">
         <v>84</v>
       </c>
-      <c r="L332" s="5"/>
+      <c r="L332" s="1">
+        <v>500</v>
+      </c>
       <c r="M332" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N332" s="1">
         <f t="shared" si="22"/>
-        <v>816</v>
+        <v>316</v>
       </c>
       <c r="O332" s="4">
         <f t="shared" si="23"/>
-        <v>0.90666666666666662</v>
+        <v>0.3511111111111111</v>
       </c>
     </row>
     <row r="333" spans="1:15">
-      <c r="A333" s="1" t="s">
+      <c r="A333" s="6" t="s">
         <v>1072</v>
       </c>
       <c r="B333" s="1" t="s">
@@ -20419,18 +20492,20 @@
       <c r="K333" s="1">
         <v>83</v>
       </c>
-      <c r="L333" s="5"/>
+      <c r="L333" s="1">
+        <v>363</v>
+      </c>
       <c r="M333" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="N333" s="1">
         <f t="shared" si="22"/>
-        <v>814</v>
+        <v>451</v>
       </c>
       <c r="O333" s="4">
         <f t="shared" si="23"/>
-        <v>0.90746934225195097</v>
+        <v>0.50278706800445927</v>
       </c>
     </row>
     <row r="334" spans="1:15">
@@ -20723,18 +20798,20 @@
       <c r="K339" s="1">
         <v>42</v>
       </c>
-      <c r="L339" s="5"/>
+      <c r="L339" s="1">
+        <v>481</v>
+      </c>
       <c r="M339" s="1">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="N339" s="1">
         <f t="shared" si="22"/>
-        <v>708</v>
+        <v>227</v>
       </c>
       <c r="O339" s="4">
         <f t="shared" si="23"/>
-        <v>0.94399999999999995</v>
+        <v>0.30266666666666664</v>
       </c>
     </row>
     <row r="340" spans="1:15">
@@ -20772,7 +20849,9 @@
       <c r="K340" s="1">
         <v>37</v>
       </c>
-      <c r="L340" s="5"/>
+      <c r="L340" s="1">
+        <v>0</v>
+      </c>
       <c r="M340" s="1">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -21218,29 +21297,31 @@
       </c>
       <c r="M349" s="1">
         <f>SUM(M8:M348)</f>
-        <v>3334649</v>
+        <v>3471209</v>
       </c>
       <c r="N349" s="1">
         <f>SUM(N8:N348)</f>
-        <v>2341991</v>
+        <v>2205431</v>
       </c>
       <c r="O349" s="4">
         <f t="shared" si="23"/>
-        <v>0.35742567669242931</v>
+        <v>0.33658441367770459</v>
       </c>
     </row>
     <row r="351" spans="1:15">
-      <c r="M351" s="6" t="s">
+      <c r="M351" s="5" t="s">
         <v>1122</v>
       </c>
-      <c r="N351" s="5"/>
+      <c r="N351" s="1">
+        <v>102879</v>
+      </c>
       <c r="O351" s="2">
         <f>SUM(N351/I349)</f>
-        <v>0</v>
+        <v>1.5700998079172992E-2</v>
       </c>
     </row>
     <row r="352" spans="1:15">
-      <c r="M352" s="6" t="s">
+      <c r="M352" s="5" t="s">
         <v>1123</v>
       </c>
       <c r="N352" s="1">
@@ -21252,7 +21333,7 @@
       </c>
     </row>
     <row r="353" spans="13:15">
-      <c r="M353" s="6" t="s">
+      <c r="M353" s="5" t="s">
         <v>1124</v>
       </c>
       <c r="N353" s="1">
@@ -21264,20 +21345,20 @@
       </c>
     </row>
     <row r="354" spans="13:15">
-      <c r="M354" s="6" t="s">
+      <c r="M354" s="5" t="s">
         <v>1125</v>
       </c>
       <c r="N354" s="1">
         <f>SUM(N351:N353)</f>
-        <v>8890</v>
+        <v>111769</v>
       </c>
       <c r="O354" s="2">
         <f>SUM(N354/I349)</f>
-        <v>1.3567576757535346E-3</v>
+        <v>1.7057755754926525E-2</v>
       </c>
     </row>
     <row r="356" spans="13:15">
-      <c r="M356" s="6" t="s">
+      <c r="M356" s="5" t="s">
         <v>1126</v>
       </c>
       <c r="N356" s="1">
@@ -21289,17 +21370,19 @@
       </c>
     </row>
     <row r="357" spans="13:15">
-      <c r="M357" s="6" t="s">
+      <c r="M357" s="5" t="s">
         <v>1127</v>
       </c>
-      <c r="N357" s="5"/>
+      <c r="N357" s="1">
+        <v>0</v>
+      </c>
       <c r="O357" s="2">
         <f>SUM(N357/I349)</f>
         <v>0</v>
       </c>
     </row>
     <row r="358" spans="13:15">
-      <c r="M358" s="6" t="s">
+      <c r="M358" s="5" t="s">
         <v>1125</v>
       </c>
       <c r="N358" s="1">
@@ -21312,25 +21395,26 @@
       </c>
     </row>
     <row r="360" spans="13:15">
-      <c r="M360" s="6" t="s">
+      <c r="M360" s="5" t="s">
         <v>1128</v>
       </c>
       <c r="N360" s="1">
         <f>SUM(N349-N354-N358)</f>
-        <v>1583630</v>
+        <v>1344191</v>
       </c>
     </row>
     <row r="361" spans="13:15">
-      <c r="M361" s="6" t="s">
+      <c r="M361" s="5" t="s">
         <v>1129</v>
       </c>
       <c r="N361" s="4">
         <f>IF(I349=0,"",N360/I349)</f>
-        <v>0.24168753183954669</v>
+        <v>0.20514527074564898</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/MomijiStore_OS/02_Analytics/SourceData/Amazon運営 KPI管理シート.xlsx
+++ b/MomijiStore_OS/02_Analytics/SourceData/Amazon運営 KPI管理シート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hide0726/Desktop/Claude Code/MomijiStore_OS/02_Analytics/SourceData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_117FCF9DC1EFC23FE5CA6B89C5A90F3FD8E83499" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_117FCF9DE99F061DA9CA6B8345EB0DF7D8E8348D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56703,10 +56703,12 @@
       <c r="M672" s="12" t="s">
         <v>1122</v>
       </c>
-      <c r="N672" s="11"/>
+      <c r="N672" s="7">
+        <v>111379</v>
+      </c>
       <c r="O672" s="8">
         <f>SUM(N672/I670)</f>
-        <v>0</v>
+        <v>1.9851265667678131E-2</v>
       </c>
     </row>
     <row r="673" spans="13:15">
@@ -56739,11 +56741,11 @@
       </c>
       <c r="N675" s="7">
         <f>SUM(N672:N674)</f>
-        <v>3836</v>
+        <v>115215</v>
       </c>
       <c r="O675" s="8">
         <f>SUM(N675/I670)</f>
-        <v>6.8369670315960196E-4</v>
+        <v>2.0534962370837732E-2</v>
       </c>
     </row>
     <row r="677" spans="13:15">
@@ -56787,7 +56789,7 @@
       </c>
       <c r="N681" s="7">
         <f>SUM(N670-N675-N679)</f>
-        <v>1220790.6499999999</v>
+        <v>1109411.6499999999</v>
       </c>
     </row>
     <row r="682" spans="13:15">
@@ -56796,7 +56798,7 @@
       </c>
       <c r="N682" s="10">
         <f>IF(I670=0,"",N681/I670)</f>
-        <v>0.21758356169266618</v>
+        <v>0.19773229602498807</v>
       </c>
     </row>
   </sheetData>
